--- a/Run_Log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
+++ b/Run_Log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
@@ -1062,7 +1062,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>53249</x:v>
+        <x:v>55818</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1121,7 +1121,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>53249</x:v>
+        <x:v>55818</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1174,7 +1174,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>53249</x:v>
+        <x:v>55818</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1230,7 +1230,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>53249</x:v>
+        <x:v>55818</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1286,7 +1286,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>53249</x:v>
+        <x:v>55818</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1401,7 +1401,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>53249</x:v>
+        <x:v>55818</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1457,7 +1457,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>53249</x:v>
+        <x:v>55818</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>56</x:v>
@@ -1513,7 +1513,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>53249</x:v>
+        <x:v>55818</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>46</x:v>
@@ -1566,7 +1566,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>53249</x:v>
+        <x:v>55818</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>

--- a/Run_Log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
+++ b/Run_Log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
@@ -1062,7 +1062,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>55818</x:v>
+        <x:v>60974</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1121,7 +1121,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>55818</x:v>
+        <x:v>60974</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1174,7 +1174,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>55818</x:v>
+        <x:v>60974</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1230,7 +1230,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>55818</x:v>
+        <x:v>60974</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1286,7 +1286,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>55818</x:v>
+        <x:v>60974</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1401,7 +1401,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>55818</x:v>
+        <x:v>60974</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1457,7 +1457,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>55818</x:v>
+        <x:v>60974</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>56</x:v>
@@ -1513,7 +1513,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>55818</x:v>
+        <x:v>60974</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>46</x:v>
@@ -1566,7 +1566,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>55818</x:v>
+        <x:v>60974</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>

--- a/Run_Log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
+++ b/Run_Log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
@@ -1062,7 +1062,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>60974</x:v>
+        <x:v>52703</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1121,7 +1121,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>60974</x:v>
+        <x:v>52703</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1174,7 +1174,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>60974</x:v>
+        <x:v>52703</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1230,7 +1230,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>60974</x:v>
+        <x:v>52703</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1286,7 +1286,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>60974</x:v>
+        <x:v>52703</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1401,7 +1401,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>60974</x:v>
+        <x:v>52703</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1457,7 +1457,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>60974</x:v>
+        <x:v>52703</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>56</x:v>
@@ -1513,7 +1513,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>60974</x:v>
+        <x:v>52703</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>46</x:v>
@@ -1566,7 +1566,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>60974</x:v>
+        <x:v>52703</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>

--- a/Run_Log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
+++ b/Run_Log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
@@ -1062,7 +1062,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>52703</x:v>
+        <x:v>60408</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1121,7 +1121,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>52703</x:v>
+        <x:v>60408</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1174,7 +1174,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>52703</x:v>
+        <x:v>60408</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1230,7 +1230,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>52703</x:v>
+        <x:v>60408</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1286,7 +1286,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>52703</x:v>
+        <x:v>60408</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1401,7 +1401,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>52703</x:v>
+        <x:v>60408</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1457,7 +1457,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>52703</x:v>
+        <x:v>60408</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>56</x:v>
@@ -1513,7 +1513,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q10" s="0">
-        <x:v>52703</x:v>
+        <x:v>60408</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
         <x:v>46</x:v>
@@ -1566,7 +1566,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>52703</x:v>
+        <x:v>60408</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>

--- a/Run_Log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
+++ b/Run_Log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
@@ -158,7 +158,10 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
-    <x:t>PASS</x:t>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIL</x:t>
   </x:si>
   <x:si>
     <x:t>SYN, ACK</x:t>
@@ -173,40 +176,16 @@
     <x:t>Connection established</x:t>
   </x:si>
   <x:si>
-    <x:t>Connection acknowledged (ACK)</x:t>
-  </x:si>
-  <x:si>
     <x:t>PSH, ACK</x:t>
   </x:si>
   <x:si>
     <x:t>Data transfer in progress</x:t>
   </x:si>
   <x:si>
-    <x:t>Client sending data</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARTIAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
     <x:t>FIN, ACK</x:t>
   </x:si>
   <x:si>
     <x:t>Closing connection (FIN-ACK)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Server closing connection</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Client closing connection</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -233,22 +212,12 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFF00"/>
-      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -275,7 +244,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="5">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -285,14 +254,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
+  <x:cellXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -302,14 +265,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -950,7 +905,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="29.996339" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1047,28 +1002,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P2" s="0">
-        <x:v>60408</x:v>
-      </x:c>
-      <x:c r="Q2" s="0">
-        <x:v>4000</x:v>
+      <x:c r="P2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q2" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:18">
@@ -1088,10 +1043,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
@@ -1103,28 +1058,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R3" s="2" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N3" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P3" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q3" s="0">
-        <x:v>60408</x:v>
-      </x:c>
-      <x:c r="R3" s="2" t="s">
-        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18">
@@ -1144,10 +1099,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
@@ -1159,28 +1114,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P4" s="0">
-        <x:v>60408</x:v>
-      </x:c>
-      <x:c r="Q4" s="0">
-        <x:v>4000</x:v>
+      <x:c r="P4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q4" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:18">
@@ -1215,28 +1170,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="P5" s="0">
-        <x:v>60408</x:v>
-      </x:c>
-      <x:c r="Q5" s="0">
-        <x:v>4000</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q5" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R5" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:18">
@@ -1256,10 +1211,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
@@ -1271,28 +1226,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="0">
-        <x:v>60408</x:v>
-      </x:c>
-      <x:c r="Q6" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R6" s="3" t="s">
-        <x:v>56</x:v>
+      <x:c r="P6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R6" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:18">
@@ -1327,7 +1282,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1347,8 +1302,8 @@
       <x:c r="Q7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R7" s="4" t="s">
-        <x:v>58</x:v>
+      <x:c r="R7" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:18">
@@ -1368,10 +1323,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
@@ -1383,28 +1338,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q8" s="0">
-        <x:v>60408</x:v>
-      </x:c>
-      <x:c r="R8" s="3" t="s">
-        <x:v>56</x:v>
+      <x:c r="P8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R8" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:18">
@@ -1424,10 +1379,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
@@ -1439,28 +1394,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P9" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q9" s="0">
-        <x:v>60408</x:v>
-      </x:c>
-      <x:c r="R9" s="3" t="s">
-        <x:v>56</x:v>
+      <x:c r="P9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R9" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:18">
@@ -1480,10 +1435,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>17</x:v>
@@ -1495,28 +1450,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P10" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q10" s="0">
-        <x:v>60408</x:v>
+      <x:c r="P10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q10" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R10" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:18">
@@ -1536,10 +1491,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
         <x:v>17</x:v>
@@ -1551,28 +1506,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M11" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N11" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O11" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P11" s="0">
-        <x:v>60408</x:v>
-      </x:c>
-      <x:c r="Q11" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R11" s="3" t="s">
-        <x:v>56</x:v>
+      <x:c r="P11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R11" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:18">
@@ -1592,10 +1547,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
         <x:v>17</x:v>
@@ -1607,7 +1562,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
         <x:v>17</x:v>
@@ -1627,8 +1582,8 @@
       <x:c r="Q12" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R12" s="4" t="s">
-        <x:v>58</x:v>
+      <x:c r="R12" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Run_Log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
+++ b/Run_Log/1/student/dungtdhe186461/TC4/GradeDetail.xlsx
@@ -158,18 +158,24 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
+    <x:t>SYN_SENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYN, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Server responding (SYN-ACK)</x:t>
+  </x:si>
+  <x:si>
     <x:t>(MISSING - not captured)</x:t>
   </x:si>
   <x:si>
     <x:t>FAIL</x:t>
   </x:si>
   <x:si>
-    <x:t>SYN, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Server responding (SYN-ACK)</x:t>
-  </x:si>
-  <x:si>
     <x:t>ACK</x:t>
   </x:si>
   <x:si>
@@ -186,6 +192,18 @@
   </x:si>
   <x:si>
     <x:t>Closing connection (FIN-ACK)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(Not validated by this test case)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RST-ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RESET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -212,7 +230,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -221,7 +239,17 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF90EE90"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -244,7 +272,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="3">
+  <x:cellStyleXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -254,8 +282,14 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -265,6 +299,14 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -891,11 +933,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:R12"/>
+  <x:dimension ref="A1:R18"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -1002,25 +1044,25 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q2" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P2" s="0">
+        <x:v>36996</x:v>
+      </x:c>
+      <x:c r="Q2" s="0">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>47</x:v>
@@ -1058,7 +1100,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
         <x:v>17</x:v>
@@ -1078,8 +1120,8 @@
       <x:c r="Q3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R3" s="2" t="s">
-        <x:v>47</x:v>
+      <x:c r="R3" s="3" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18">
@@ -1099,10 +1141,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
@@ -1114,7 +1156,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
         <x:v>17</x:v>
@@ -1134,8 +1176,8 @@
       <x:c r="Q4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R4" s="2" t="s">
-        <x:v>47</x:v>
+      <x:c r="R4" s="3" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:18">
@@ -1155,10 +1197,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
@@ -1170,7 +1212,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
         <x:v>17</x:v>
@@ -1190,8 +1232,8 @@
       <x:c r="Q5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R5" s="2" t="s">
-        <x:v>47</x:v>
+      <x:c r="R5" s="3" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:18">
@@ -1211,10 +1253,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
@@ -1226,7 +1268,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
         <x:v>17</x:v>
@@ -1246,8 +1288,8 @@
       <x:c r="Q6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R6" s="2" t="s">
-        <x:v>47</x:v>
+      <x:c r="R6" s="3" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:18">
@@ -1267,10 +1309,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
@@ -1282,7 +1324,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1302,8 +1344,8 @@
       <x:c r="Q7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R7" s="2" t="s">
-        <x:v>47</x:v>
+      <x:c r="R7" s="3" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:18">
@@ -1323,10 +1365,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
@@ -1338,7 +1380,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
         <x:v>17</x:v>
@@ -1358,8 +1400,8 @@
       <x:c r="Q8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R8" s="2" t="s">
-        <x:v>47</x:v>
+      <x:c r="R8" s="3" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:18">
@@ -1379,10 +1421,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
@@ -1394,7 +1436,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
         <x:v>17</x:v>
@@ -1414,8 +1456,8 @@
       <x:c r="Q9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R9" s="2" t="s">
-        <x:v>47</x:v>
+      <x:c r="R9" s="3" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:18">
@@ -1435,10 +1477,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>17</x:v>
@@ -1450,7 +1492,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
         <x:v>17</x:v>
@@ -1470,8 +1512,8 @@
       <x:c r="Q10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R10" s="2" t="s">
-        <x:v>47</x:v>
+      <x:c r="R10" s="3" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:18">
@@ -1491,10 +1533,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
         <x:v>17</x:v>
@@ -1506,7 +1548,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
         <x:v>17</x:v>
@@ -1526,8 +1568,8 @@
       <x:c r="Q11" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R11" s="2" t="s">
-        <x:v>47</x:v>
+      <x:c r="R11" s="3" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:18">
@@ -1547,10 +1589,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
         <x:v>17</x:v>
@@ -1562,28 +1604,364 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R12" s="3" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:18">
+      <x:c r="A13" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L13" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M13" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N13" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P13" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q13" s="0">
+        <x:v>36996</x:v>
+      </x:c>
+      <x:c r="R13" s="4" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:18">
+      <x:c r="A14" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K14" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L14" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="L12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R12" s="2" t="s">
-        <x:v>47</x:v>
+      <x:c r="M14" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N14" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P14" s="0">
+        <x:v>54552</x:v>
+      </x:c>
+      <x:c r="Q14" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R14" s="4" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:18">
+      <x:c r="A15" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K15" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L15" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M15" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N15" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P15" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q15" s="0">
+        <x:v>54552</x:v>
+      </x:c>
+      <x:c r="R15" s="4" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:18">
+      <x:c r="A16" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K16" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L16" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M16" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N16" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P16" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q16" s="0">
+        <x:v>45850</x:v>
+      </x:c>
+      <x:c r="R16" s="4" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:18">
+      <x:c r="A17" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K17" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L17" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="M17" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N17" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P17" s="0">
+        <x:v>58620</x:v>
+      </x:c>
+      <x:c r="Q17" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R17" s="4" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:18">
+      <x:c r="A18" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K18" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="L18" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="M18" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N18" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P18" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q18" s="0">
+        <x:v>58620</x:v>
+      </x:c>
+      <x:c r="R18" s="4" t="s">
+        <x:v>61</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
